--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_nuble.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_nuble.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.49200468636205</v>
+      </c>
+      <c r="C2">
         <v>29.47658402203857</v>
-      </c>
-      <c r="C2">
-        <v>27.49200468636205</v>
       </c>
       <c r="D2">
         <v>3.392523364485981</v>
       </c>
       <c r="E2">
-        <v>18.77865136240537</v>
+        <v>17.51433513709788</v>
       </c>
       <c r="F2">
-        <v>63.70701350049674</v>
+        <v>63.70701350049676</v>
       </c>
       <c r="G2">
-        <v>17.51433513709787</v>
+        <v>18.77865136240538</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.84350935093509</v>
+      </c>
+      <c r="C3">
         <v>34.43344334433444</v>
-      </c>
-      <c r="C3">
-        <v>28.84350935093509</v>
       </c>
       <c r="D3">
         <v>2.904153354632588</v>
       </c>
       <c r="E3">
-        <v>21.08897966058871</v>
+        <v>17.66538931233419</v>
       </c>
       <c r="F3">
         <v>61.2456310270771</v>
       </c>
       <c r="G3">
-        <v>17.66538931233419</v>
+        <v>21.08897966058871</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>28.6705093959417</v>
+      </c>
+      <c r="C4">
         <v>23.67964759360795</v>
-      </c>
-      <c r="C4">
-        <v>28.6705093959417</v>
       </c>
       <c r="D4">
         <v>4.223035820304769</v>
       </c>
       <c r="E4">
-        <v>15.54290987388496</v>
+        <v>18.81882497693017</v>
       </c>
       <c r="F4">
         <v>65.63826514918487</v>
       </c>
       <c r="G4">
-        <v>18.81882497693017</v>
+        <v>15.54290987388496</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>28.26669917113603</v>
+      </c>
+      <c r="C5">
         <v>35.21452949780595</v>
-      </c>
-      <c r="C5">
-        <v>28.26669917113603</v>
       </c>
       <c r="D5">
         <v>2.839736933194877</v>
       </c>
       <c r="E5">
-        <v>21.54041157172681</v>
+        <v>17.29048613182225</v>
       </c>
       <c r="F5">
         <v>61.16910229645094</v>
       </c>
       <c r="G5">
-        <v>17.29048613182225</v>
+        <v>21.54041157172681</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>28.21922667612629</v>
+      </c>
+      <c r="C6">
         <v>34.24973394820859</v>
-      </c>
-      <c r="C6">
-        <v>28.21922667612629</v>
       </c>
       <c r="D6">
         <v>2.919730709476955</v>
       </c>
       <c r="E6">
-        <v>21.08078602620088</v>
+        <v>17.36899563318777</v>
       </c>
       <c r="F6">
         <v>61.55021834061135</v>
       </c>
       <c r="G6">
-        <v>17.36899563318777</v>
+        <v>21.08078602620088</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>26.71415850400712</v>
+      </c>
+      <c r="C7">
         <v>36.47118687189925</v>
-      </c>
-      <c r="C7">
-        <v>26.71415850400712</v>
       </c>
       <c r="D7">
         <v>2.741890477851413</v>
       </c>
       <c r="E7">
-        <v>22.3495478640474</v>
+        <v>16.37043966323667</v>
       </c>
       <c r="F7">
         <v>61.28001247271594</v>
       </c>
       <c r="G7">
-        <v>16.37043966323667</v>
+        <v>22.3495478640474</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.23184910860391</v>
+      </c>
+      <c r="C8">
         <v>41.67599689949186</v>
-      </c>
-      <c r="C8">
-        <v>28.23184910860391</v>
       </c>
       <c r="D8">
         <v>2.399462698904733</v>
       </c>
       <c r="E8">
-        <v>24.52858880778589</v>
+        <v>16.61597729115978</v>
       </c>
       <c r="F8">
         <v>58.85543390105434</v>
       </c>
       <c r="G8">
-        <v>16.61597729115978</v>
+        <v>24.52858880778589</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>27.04052780395853</v>
+      </c>
+      <c r="C9">
         <v>36.70122525918945</v>
-      </c>
-      <c r="C9">
-        <v>27.04052780395853</v>
       </c>
       <c r="D9">
         <v>2.724704673857216</v>
       </c>
       <c r="E9">
-        <v>22.41409083059921</v>
+        <v>16.51413112300697</v>
       </c>
       <c r="F9">
         <v>61.07177804639383</v>
       </c>
       <c r="G9">
-        <v>16.51413112300697</v>
+        <v>22.41409083059921</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.25720546098096</v>
+      </c>
+      <c r="C10">
         <v>34.07213888420698</v>
-      </c>
-      <c r="C10">
-        <v>28.25720546098096</v>
       </c>
       <c r="D10">
         <v>2.934949295077912</v>
       </c>
       <c r="E10">
-        <v>20.98951303083792</v>
+        <v>17.40733049527567</v>
       </c>
       <c r="F10">
         <v>61.60315647388639</v>
       </c>
       <c r="G10">
-        <v>17.40733049527567</v>
+        <v>20.98951303083792</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>27.53031101739588</v>
+      </c>
+      <c r="C11">
         <v>37.4934106483922</v>
-      </c>
-      <c r="C11">
-        <v>27.53031101739588</v>
       </c>
       <c r="D11">
         <v>2.66713532513181</v>
       </c>
       <c r="E11">
-        <v>22.72001277751158</v>
+        <v>16.68263855614119</v>
       </c>
       <c r="F11">
         <v>60.59734866634723</v>
       </c>
       <c r="G11">
-        <v>16.68263855614119</v>
+        <v>22.72001277751158</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>23.98293963254593</v>
+      </c>
+      <c r="C12">
         <v>49.80314960629921</v>
-      </c>
-      <c r="C12">
-        <v>23.98293963254593</v>
       </c>
       <c r="D12">
         <v>2.007905138339921</v>
       </c>
       <c r="E12">
-        <v>28.65773079101378</v>
+        <v>13.80026430054748</v>
       </c>
       <c r="F12">
         <v>57.54200490843874</v>
       </c>
       <c r="G12">
-        <v>13.80026430054748</v>
+        <v>28.65773079101378</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>27.68435885392203</v>
+      </c>
+      <c r="C13">
         <v>37.80178487552842</v>
-      </c>
-      <c r="C13">
-        <v>27.68435885392203</v>
       </c>
       <c r="D13">
         <v>2.645377733598409</v>
       </c>
       <c r="E13">
-        <v>22.84287011807448</v>
+        <v>16.72910990009083</v>
       </c>
       <c r="F13">
         <v>60.42801998183469</v>
       </c>
       <c r="G13">
-        <v>16.72910990009083</v>
+        <v>22.84287011807448</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>24.73622508792497</v>
+      </c>
+      <c r="C14">
         <v>44.84173505275498</v>
-      </c>
-      <c r="C14">
-        <v>24.73622508792497</v>
       </c>
       <c r="D14">
         <v>2.230065359477124</v>
       </c>
       <c r="E14">
-        <v>26.44313861043899</v>
+        <v>14.58693397856896</v>
       </c>
       <c r="F14">
         <v>58.96992741099205</v>
       </c>
       <c r="G14">
-        <v>14.58693397856896</v>
+        <v>26.44313861043899</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>26.5778623533143</v>
+      </c>
+      <c r="C15">
         <v>44.3070091975896</v>
-      </c>
-      <c r="C15">
-        <v>26.5778623533143</v>
       </c>
       <c r="D15">
         <v>2.25697924123121</v>
       </c>
       <c r="E15">
-        <v>25.92798812175205</v>
+        <v>15.55308092056422</v>
       </c>
       <c r="F15">
-        <v>58.51893095768375</v>
+        <v>58.51893095768374</v>
       </c>
       <c r="G15">
-        <v>15.55308092056422</v>
+        <v>25.92798812175204</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>28.2934963868816</v>
+      </c>
+      <c r="C16">
         <v>48.80489160644802</v>
-      </c>
-      <c r="C16">
-        <v>28.2934963868816</v>
       </c>
       <c r="D16">
         <v>2.048974943052392</v>
       </c>
       <c r="E16">
-        <v>27.55806654111739</v>
+        <v>15.97614563716258</v>
       </c>
       <c r="F16">
         <v>56.46578782172003</v>
       </c>
       <c r="G16">
-        <v>15.97614563716258</v>
+        <v>27.55806654111739</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>23.36571278550801</v>
+      </c>
+      <c r="C17">
         <v>38.35652402205304</v>
-      </c>
-      <c r="C17">
-        <v>23.36571278550801</v>
       </c>
       <c r="D17">
         <v>2.607118412046543</v>
       </c>
       <c r="E17">
-        <v>23.71753246753247</v>
+        <v>14.44805194805195</v>
       </c>
       <c r="F17">
         <v>61.83441558441558</v>
       </c>
       <c r="G17">
-        <v>14.44805194805195</v>
+        <v>23.71753246753247</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>27.58543291622243</v>
+      </c>
+      <c r="C18">
         <v>33.87576454744403</v>
-      </c>
-      <c r="C18">
-        <v>27.58543291622243</v>
       </c>
       <c r="D18">
         <v>2.951962895477886</v>
       </c>
       <c r="E18">
-        <v>20.9807465072635</v>
+        <v>17.08486828386738</v>
       </c>
       <c r="F18">
         <v>61.93438520886912</v>
       </c>
       <c r="G18">
-        <v>17.08486828386738</v>
+        <v>20.9807465072635</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>30.04434589800443</v>
+      </c>
+      <c r="C19">
         <v>28.17073170731707</v>
-      </c>
-      <c r="C19">
-        <v>30.04434589800443</v>
       </c>
       <c r="D19">
         <v>3.54978354978355</v>
       </c>
       <c r="E19">
-        <v>17.80533949968468</v>
+        <v>18.98955924602341</v>
       </c>
       <c r="F19">
         <v>63.20510125429193</v>
       </c>
       <c r="G19">
-        <v>18.98955924602341</v>
+        <v>17.80533949968468</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>24.70023980815348</v>
+      </c>
+      <c r="C20">
         <v>42.9761453994699</v>
-      </c>
-      <c r="C20">
-        <v>24.70023980815348</v>
       </c>
       <c r="D20">
         <v>2.326872246696035</v>
       </c>
       <c r="E20">
-        <v>25.63041023710953</v>
+        <v>14.73089951072639</v>
       </c>
       <c r="F20">
         <v>59.6386902521641</v>
       </c>
       <c r="G20">
-        <v>14.73089951072639</v>
+        <v>25.63041023710953</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>30.12987012987013</v>
+      </c>
+      <c r="C21">
         <v>38.34415584415584</v>
-      </c>
-      <c r="C21">
-        <v>30.12987012987013</v>
       </c>
       <c r="D21">
         <v>2.607959356477561</v>
       </c>
       <c r="E21">
+        <v>17.88398535363268</v>
+      </c>
+      <c r="F21">
+        <v>59.35633069955675</v>
+      </c>
+      <c r="G21">
         <v>22.75968394681056</v>
-      </c>
-      <c r="F21">
-        <v>59.35633069955676</v>
-      </c>
-      <c r="G21">
-        <v>17.88398535363268</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>26.73163940132266</v>
+      </c>
+      <c r="C22">
         <v>35.17809490660169</v>
-      </c>
-      <c r="C22">
-        <v>26.73163940132266</v>
       </c>
       <c r="D22">
         <v>2.842678100263852</v>
       </c>
       <c r="E22">
-        <v>21.72697957721246</v>
+        <v>16.51021139376567</v>
       </c>
       <c r="F22">
         <v>61.76280902902185</v>
       </c>
       <c r="G22">
-        <v>16.51021139376567</v>
+        <v>21.72697957721246</v>
       </c>
     </row>
   </sheetData>
